--- a/artfynd/A 32301-2023 artfynd.xlsx
+++ b/artfynd/A 32301-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32301-2023 artfynd.xlsx
+++ b/artfynd/A 32301-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112182879</v>
+        <v>112181719</v>
       </c>
       <c r="B2" t="n">
-        <v>96692</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>773961</v>
+        <v>774037</v>
       </c>
       <c r="R2" t="n">
-        <v>7252979</v>
+        <v>7252974</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112182870</v>
+        <v>112182868</v>
       </c>
       <c r="B3" t="n">
-        <v>96692</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>773961</v>
+        <v>773705</v>
       </c>
       <c r="R3" t="n">
-        <v>7252980</v>
+        <v>7252824</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112181719</v>
+        <v>112182870</v>
       </c>
       <c r="B4" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774037</v>
+        <v>773961</v>
       </c>
       <c r="R4" t="n">
-        <v>7252974</v>
+        <v>7252980</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1005,6 +990,218 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112182881</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kalamark, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>773696</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7252835</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112182887</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kalamark, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>773705</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7252847</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32301-2023 artfynd.xlsx
+++ b/artfynd/A 32301-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112181719</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182868</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182870</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182881</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,8 +1227,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182887</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>